--- a/자습실5.xlsx
+++ b/자습실5.xlsx
@@ -1,185 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fileVersion appName="HCell" lastEdited="12.0" lowestEdited="12.0" rupBuild="0.535"/>
-  <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\GitHub\cipchecker\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="22788" windowHeight="8112"/>
-  </x:bookViews>
-  <x:sheets>
-    <x:sheet name="Sheet1" sheetId="1" r:id="rId4"/>
-  </x:sheets>
-  <x:calcPr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" mc:Ignorable="hs" hs:hclCalcId="904"/>
-</x:workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <x:si>
-    <x:t>CIP3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CIP2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>학번</x:t>
-  </x:si>
-</x:sst>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="7">
-    <x:font>
-      <x:name val="맑은 고딕"/>
-      <x:sz val="11"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="맑은 고딕"/>
-      <x:sz val="11"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="맑은 고딕"/>
-      <x:sz val="11"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="맑은 고딕"/>
-      <x:sz val="11"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="맑은 고딕"/>
-      <x:sz val="11"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="맑은 고딕"/>
-      <x:sz val="11"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="맑은 고딕"/>
-      <x:sz val="11"/>
-      <x:color rgb="ff000000"/>
-      <x:b val="1"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="2">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-  </x:fills>
-  <x:borders count="2">
-    <x:border>
-      <x:left>
-        <x:color rgb="ff000000"/>
-      </x:left>
-      <x:right>
-        <x:color rgb="ff000000"/>
-      </x:right>
-      <x:top>
-        <x:color auto="1"/>
-      </x:top>
-      <x:bottom>
-        <x:color rgb="ff000000"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color auto="1"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color auto="1"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color auto="1"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color auto="1"/>
-      </x:bottom>
-    </x:border>
-  </x:borders>
-  <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-  </x:cellStyleXfs>
-  <x:cellXfs count="2">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="top"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="top"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-  </x:cellXfs>
-  <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </x:cellStyles>
-  <x:dxfs count="0"/>
-  <x:tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-</x:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -422,31 +414,65 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:D1"/>
-  <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
-  <x:sheetData>
-    <x:row r="1" spans="1:4">
-      <x:c r="A1" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B1" s="1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C1" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D1" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>학번</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>CIP2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>CIP3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>21008</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>김선민</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>자습실5</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>자습실5</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/자습실5.xlsx
+++ b/자습실5.xlsx
@@ -1,177 +1,185 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
+<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:fileVersion appName="HCell" lastEdited="12.0" lowestEdited="12.0" rupBuild="0.535"/>
+  <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\GitHub\cipchecker\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <x:bookViews>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="22788" windowHeight="8112"/>
+  </x:bookViews>
+  <x:sheets>
+    <x:sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+  </x:sheets>
+  <x:calcPr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" mc:Ignorable="hs" hs:hclCalcId="904"/>
+</x:workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+  <x:si>
+    <x:t>학번</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CIP3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CIP2</x:t>
+  </x:si>
+</x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
-  </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-  </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-  </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
-</styleSheet>
+<x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:fonts count="7">
+    <x:font>
+      <x:name val="맑은 고딕"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="맑은 고딕"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="맑은 고딕"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="맑은 고딕"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="맑은 고딕"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="맑은 고딕"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="맑은 고딕"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+      <x:b val="1"/>
+    </x:font>
+  </x:fonts>
+  <x:fills count="2">
+    <x:fill>
+      <x:patternFill patternType="none"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="gray125"/>
+    </x:fill>
+  </x:fills>
+  <x:borders count="2">
+    <x:border>
+      <x:left>
+        <x:color rgb="ff000000"/>
+      </x:left>
+      <x:right>
+        <x:color rgb="ff000000"/>
+      </x:right>
+      <x:top>
+        <x:color auto="1"/>
+      </x:top>
+      <x:bottom>
+        <x:color rgb="ff000000"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color auto="1"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color auto="1"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color auto="1"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color auto="1"/>
+      </x:bottom>
+    </x:border>
+  </x:borders>
+  <x:cellStyleXfs count="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+  </x:cellStyleXfs>
+  <x:cellXfs count="2">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="top"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="top"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </x:cellXfs>
+  <x:cellStyles count="1">
+    <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </x:cellStyles>
+  <x:dxfs count="0"/>
+  <x:tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+</x:styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -414,65 +422,31 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>학번</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>이름</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>CIP2</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>CIP3</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>21008</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>김선민</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>자습실5</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>자습실5</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr codeName="Sheet1"/>
+  <x:dimension ref="A1:D1"/>
+  <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
+  <x:sheetData>
+    <x:row r="1" spans="1:4">
+      <x:c r="A1" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
+</x:worksheet>
 </file>